--- a/data/trans_orig/IQ2606_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>31594</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>47027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30621</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>45765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>65172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87911</t>
+          <t>88655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21140</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>37334</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42009</t>
+          <t>41808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152262</t>
+          <t>150614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184008</t>
+          <t>186044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157520</t>
+          <t>157377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193342</t>
+          <t>192506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317947</t>
+          <t>317531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366164</t>
+          <t>366466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>77587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105645</t>
+          <t>104643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73977</t>
+          <t>73453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101613</t>
+          <t>102891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160598</t>
+          <t>162094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199292</t>
+          <t>200917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>69485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95923</t>
+          <t>96289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63350</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>91604</t>
+          <t>91574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>140925</t>
+          <t>140881</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180633</t>
+          <t>179435</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34023</t>
+          <t>35359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>30807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>50733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53405</t>
+          <t>54000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>80427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87048</t>
+          <t>86366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80434</t>
+          <t>81359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110188</t>
+          <t>109241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148034</t>
+          <t>148569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187407</t>
+          <t>187733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64833</t>
+          <t>64344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86415</t>
+          <t>85790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55834</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76797</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126891</t>
+          <t>127126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155984</t>
+          <t>157087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>34634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52660</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92793</t>
+          <t>93395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>20852</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>61842</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>262610</t>
+          <t>263257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>303782</t>
+          <t>302972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>257497</t>
+          <t>254823</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>296168</t>
+          <t>297946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>530215</t>
+          <t>529680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>591581</t>
+          <t>591195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168168</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123508</t>
+          <t>122873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157862</t>
+          <t>157381</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260596</t>
+          <t>260665</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>310653</t>
+          <t>307211</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>102509</t>
+          <t>103738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>135199</t>
+          <t>135123</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103730</t>
+          <t>102632</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135627</t>
+          <t>136613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>216269</t>
+          <t>215834</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>264949</t>
+          <t>262356</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51398</t>
+          <t>49874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76136</t>
+          <t>76029</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>88480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120457</t>
+          <t>120891</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>86629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109380</t>
+          <t>110564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144208</t>
+          <t>145358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204686</t>
+          <t>207434</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252582</t>
+          <t>252314</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51547</t>
+          <t>51231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21790</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44961</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14194</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24468</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182663</t>
+          <t>180679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217024</t>
+          <t>215165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>188903</t>
+          <t>189398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223759</t>
+          <t>224765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>379000</t>
+          <t>381291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>430693</t>
+          <t>431174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120574</t>
+          <t>123172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152795</t>
+          <t>154981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129485</t>
+          <t>130220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161965</t>
+          <t>163042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263132</t>
+          <t>261118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307896</t>
+          <t>305978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>52248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>76455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45628</t>
+          <t>45704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68498</t>
+          <t>69528</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103416</t>
+          <t>104015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137051</t>
+          <t>136691</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>20054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35523</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>41866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64013</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40558</t>
+          <t>40407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63582</t>
+          <t>62565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>88033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119517</t>
+          <t>121017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>78166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98444</t>
+          <t>98649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109820</t>
+          <t>110435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171096</t>
+          <t>171412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203295</t>
+          <t>203117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34324</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53074</t>
+          <t>52817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60315</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79480</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107366</t>
+          <t>107151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24831</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24354</t>
+          <t>24109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>38737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>289621</t>
+          <t>289816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>333482</t>
+          <t>332066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>302122</t>
+          <t>303266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>347948</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>602629</t>
+          <t>601467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>665812</t>
+          <t>660577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176306</t>
+          <t>177377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215474</t>
+          <t>215385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195438</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>237246</t>
+          <t>236489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>386831</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441894</t>
+          <t>442247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>73072</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>103446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>75582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>104913</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>157603</t>
+          <t>157755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>197887</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69743</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>91152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132218</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>170907</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10171</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>46914</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>38493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59853</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>73475</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99830</t>
+          <t>99704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44481</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55182</t>
+          <t>56140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77612</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89483</t>
+          <t>89278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117657</t>
+          <t>115472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15978</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6174</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21160</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27744</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>44492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>86420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145770</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>71439</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107507</t>
+          <t>105985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>138056</t>
+          <t>136862</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,44 +9050,44 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
